--- a/schools-presentations/A Gymnasiou/kahoot/A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου.xlsx
+++ b/schools-presentations/A Gymnasiou/kahoot/A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="R2b7a74a8286f4d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="Rde67ee7ac1474e95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +55,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF4CC"/>
+        <x:fgColor rgb="FFFFF1C7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -340,30 +340,30 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="31" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="31" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Question - max 95 characters</x:v>
+        <x:v>Question - max 120 characters</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>Answer 1 - max 60 characters</x:v>
+        <x:v>Answer 1 - max 75 characters</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Answer 2 - max 60 characters</x:v>
+        <x:v>Answer 2 - max 75 characters</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Answer 3 - max 60 characters</x:v>
+        <x:v>Answer 3 - max 75 characters</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Answer 4 - max 60 characters</x:v>
+        <x:v>Answer 4 - max 75 characters</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
         <x:v>Time limit (sec)</x:v>
@@ -372,44 +372,44 @@
         <x:v>Correct answer(s)</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="58" customHeight="1">
+    <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Τι κάνει η εντολή Forward;</x:v>
+        <x:v>Ποια εντολή στέλνει ένα υπάρχον μήνυμα σε νέο παραλήπτη;</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Προωθεί ένα μήνυμα σε νέο παραλήπτη</x:v>
+        <x:v>Reply</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Απαντά μόνο στον αποστολέα</x:v>
+        <x:v>Reply all</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Διαγράφει το μήνυμα</x:v>
+        <x:v>Forward</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>Μεταφέρει το μήνυμα στα Πρόχειρα</x:v>
+        <x:v>Draft</x:v>
       </x:c>
       <x:c r="F2" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>Σε ποιο πεδίο γράφουμε τον κύριο παραλήπτη;</x:v>
+        <x:v>Σε ποιο πεδίο γράφουμε τον κύριο παραλήπτη που αναμένεται να ενεργήσει;</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Στο To</x:v>
+        <x:v>To</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Στο Cc</x:v>
+        <x:v>Cc</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Στο Bcc</x:v>
+        <x:v>Bcc</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>Στο Subject</x:v>
+        <x:v>Subject</x:v>
       </x:c>
       <x:c r="F3" s="14" t="n">
         <x:v>20</x:v>
@@ -418,67 +418,67 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="58" customHeight="1">
+    <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>Τι σημαίνει Cc σε ένα μήνυμα;</x:v>
+        <x:v>Τι σημαίνει η χρήση του Cc σε ένα μήνυμα;</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Κοινοποίηση σε επιπλέον παραλήπτες</x:v>
+        <x:v>Ο παραλήπτης δεν βλέπει κανέναν άλλο</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Κρυφή διαγραφή του μηνύματος</x:v>
+        <x:v>Το μήνυμα αποθηκεύεται ως πρόχειρο</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Αποθήκευση στα Πρόχειρα</x:v>
+        <x:v>Ο παραλήπτης πρέπει πάντα να απαντήσει</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Απάντηση μόνο στον αποστολέα</x:v>
+        <x:v>Στέλνεται φανερό αντίγραφο για ενημέρωση</x:v>
       </x:c>
       <x:c r="F4" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G4" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="11" t="str">
-        <x:v>Τι σημαίνει Bcc σε ένα μήνυμα;</x:v>
+        <x:v>Τι σημαίνει η χρήση του Bcc;</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Κρυφή κοινοποίηση σε επιπλέον παραλήπτες</x:v>
+        <x:v>Απάντηση σε όλους τους παραλήπτες</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>Αποστολή χωρίς θέμα</x:v>
+        <x:v>Κρυφή κοινοποίηση σε επιπλέον παραλήπτη</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>Απάντηση σε όλους</x:v>
+        <x:v>Προώθηση χωρίς το αρχικό μήνυμα</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>Προώθηση χωρίς κείμενο</x:v>
+        <x:v>Αποστολή μηνύματος χωρίς θέμα</x:v>
       </x:c>
       <x:c r="F5" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="11" t="str">
-        <x:v>Οι παραλήπτες στο Cc είναι ορατοί στους άλλους παραλήπτες;</x:v>
+        <x:v>Τι ισχύει για τις διευθύνσεις που βρίσκονται στο Cc;</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Ναι, οι διευθύνσεις τους είναι ορατές</x:v>
+        <x:v>Είναι ορατές στους άλλους παραλήπτες</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Όχι, είναι πάντα κρυφοί</x:v>
+        <x:v>Είναι ορατές μόνο στον αποστολέα</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Μόνο στον αποστολέα του μηνύματος</x:v>
+        <x:v>Κρύβονται μόλις ανοίξει το μήνυμα</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Μόνο αν απαντήσουν</x:v>
+        <x:v>Εμφανίζονται μόνο μετά από Reply</x:v>
       </x:c>
       <x:c r="F6" s="14" t="n">
         <x:v>30</x:v>
@@ -487,119 +487,119 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="58" customHeight="1">
+    <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="11" t="str">
-        <x:v>Οι παραλήπτες στο Bcc είναι ορατοί στους άλλους παραλήπτες;</x:v>
+        <x:v>Τι ισχύει για έναν παραλήπτη που βρίσκεται στο Bcc;</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Ναι, εμφανίζονται μαζί με το To</x:v>
+        <x:v>Βλέπει μόνο το θέμα και όχι το μήνυμα</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Όχι, παραμένουν κρυφοί</x:v>
+        <x:v>Εμφανίζεται στο Cc μετά την αποστολή</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>Μόνο στους παραλήπτες του Cc</x:v>
+        <x:v>Πρέπει να απαντήσει σε όλους</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Μόνο όταν γίνει Forward</x:v>
+        <x:v>Η διεύθυνσή του δεν φαίνεται στους άλλους παραλήπτες</x:v>
       </x:c>
       <x:c r="F7" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="11" t="str">
-        <x:v>Πότε είναι χρήσιμο το Bcc;</x:v>
+        <x:v>Πότε είναι καταλληλότερο το Bcc;</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Όταν δεν θέλουμε να φαίνονται οι άλλοι παραλήπτες</x:v>
+        <x:v>Όταν θέλουμε ο κύριος παραλήπτης να απαντήσει</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Όταν θέλουμε να διαγράψουμε το μήνυμα</x:v>
+        <x:v>Όταν στέλνουμε μόνο στον εαυτό μας</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Όταν θέλουμε να απαντήσουμε μόνο στον αποστολέα</x:v>
+        <x:v>Όταν δεν πρέπει να αποκαλυφθούν οι διευθύνσεις των παραληπτών</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Όταν το μήνυμα δεν έχει παραλήπτη</x:v>
+        <x:v>Όταν θέλουμε όλοι να γνωρίζουν ποιος ενημερώθηκε</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="11" t="str">
-        <x:v>Τι μπορεί να προστεθεί όταν προωθούμε ένα μήνυμα;</x:v>
+        <x:v>Τι μπορούμε να προσθέσουμε όταν κάνουμε Forward;</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Νέος παραλήπτης και δικό μας εισαγωγικό κείμενο</x:v>
+        <x:v>Μόνο τον αρχικό αποστολέα</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Μόνο ο αρχικός αποστολέας</x:v>
+        <x:v>Νέο παραλήπτη και σύντομο εισαγωγικό σχόλιο</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Μόνο μία κρυφή επαφή</x:v>
+        <x:v>Μόνο παραλήπτες που υπήρχαν ήδη</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>Κανένα νέο στοιχείο</x:v>
+        <x:v>Μόνο μία διεύθυνση Bcc</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="13" t="str">
-        <x:v>Άννα στο To, Βασίλης στο Cc, Γιώργος στο Bcc. Ποιοι βλέπουν τον Γιώργο;</x:v>
+        <x:v>Άννα στο To, Βασίλης στο Cc, Γιώργος στο Bcc. Ποιοι βλέπουν τη διεύθυνση του Γιώργου;</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Η Άννα και ο Βασίλης</x:v>
+        <x:v>Κανένας από τους άλλους παραλήπτες</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Μόνο η Άννα</x:v>
+        <x:v>Μόνο η Άννα, επειδή βρίσκεται στο To</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>Μόνο ο Βασίλης</x:v>
+        <x:v>Μόνο ο Βασίλης, επειδή βρίσκεται στο Cc</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>Κανένας άλλος παραλήπτης</x:v>
+        <x:v>Η Άννα και ο Βασίλης, αλλά όχι ο αποστολέας</x:v>
       </x:c>
       <x:c r="F10" s="15" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="58" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="13" t="str">
-        <x:v>Στέλνεις ανακοίνωση σε 40 πελάτες χωρίς να βλέπουν τις διευθύνσεις τους. Τι χρησιμοποιείς;</x:v>
+        <x:v>Ανακοίνωση πάει σε 40 γονείς χωρίς αποκάλυψη διευθύνσεων. Ποια ρύθμιση είναι ασφαλέστερη;</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>Όλους στο To</x:v>
+        <x:v>Όλοι στο To και ο εκπαιδευτικός στο Cc</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>Όλους στο Cc</x:v>
+        <x:v>Όλοι στο Cc και κενό το To</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>Όλους στο Bcc</x:v>
+        <x:v>Forward ξεχωριστά χωρίς έλεγχο παραληπτών</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Forward σε κάθε μήνυμα</x:v>
+        <x:v>Μία δική μας διεύθυνση στο To και οι γονείς στο Bcc</x:v>
       </x:c>
       <x:c r="F11" s="15" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G11" s="15" t="str">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
